--- a/output/pdf_financials_xlsx/ANT.xlsx
+++ b/output/pdf_financials_xlsx/ANT.xlsx
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.475202</v>
+        <v>0.039394</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.744004</v>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.217904</v>
+        <v>-0.217904</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.352502</v>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.217904</v>
+        <v>-0.217904</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.352502</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>10.8952</v>
+        <v>-10.8952</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>-17.6251</v>
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.475202</v>
+        <v>0.039394</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.744004</v>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.475202</v>
+        <v>0.039394</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.744004</v>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>54.14497413731424</v>
+        <v>653.1400720921968</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-52.62095365078683</v>
@@ -2201,16 +2201,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.009875999999999999</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.009875999999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="93">
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>0.217904</v>
+        <v>-0.217904</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.352502</v>
@@ -3634,7 +3634,11 @@
           <t>Share-based payments reserve 5</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -4100,7 +4104,11 @@
           <t>Share-based payments reserve 6</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -4426,7 +4434,11 @@
           <t>Share‐based payments reserve 6</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="n">
         <v>0.009875999999999999</v>
       </c>
@@ -7840,7 +7852,7 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0.217904</v>
+        <v>-0.217904</v>
       </c>
       <c r="F134" s="5" t="n">
         <v>-0.352502</v>

--- a/output/pdf_financials_xlsx/ANT.xlsx
+++ b/output/pdf_financials_xlsx/ANT.xlsx
@@ -605,16 +605,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.034942</v>
+        <v>0.173167</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.033079</v>
+        <v>0.260587</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.075654</v>
+        <v>0.5234259999999999</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.15933</v>
+        <v>0.347439</v>
       </c>
     </row>
     <row r="11">
@@ -624,13 +624,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.034942</v>
+        <v>-0.173167</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.033079</v>
+        <v>-0.260587</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.075654</v>
+        <v>-0.5234259999999999</v>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
@@ -1083,16 +1083,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.13392</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.004718</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.102303</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.142845</v>
       </c>
     </row>
     <row r="35">
@@ -1121,16 +1121,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.415</v>
+        <v>0.54892</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.21</v>
+        <v>0.214718</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.102303</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.142845</v>
       </c>
     </row>
     <row r="37">
@@ -1349,16 +1349,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.157124</v>
+        <v>0.023204</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.024443</v>
+        <v>0.019725</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.321574</v>
+        <v>0.219271</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.173935</v>
+        <v>0.03109</v>
       </c>
     </row>
     <row r="49">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">

--- a/output/pdf_financials_xlsx/ANT.xlsx
+++ b/output/pdf_financials_xlsx/ANT.xlsx
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>-0.217904</v>
+        <v>0.217904</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.352502</v>
@@ -2632,7 +2632,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.144529</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -4804,7 +4804,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -4878,7 +4882,11 @@
           <t>Net funds received from private placement</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -5806,7 +5814,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E77" s="5" t="n">
         <v>0.217904</v>
       </c>
@@ -7812,7 +7824,11 @@
           <t>Income taxes recovery (expense) 8</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E133" s="5" t="n">
         <v>-0.039394</v>
       </c>
